--- a/config/limit_drops/random_drops.xlsx
+++ b/config/limit_drops/random_drops.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Probability of dropped items</t>
+          <t>掉落物品概率</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
